--- a/Data/ICC005/ICC005-ATP.xlsx
+++ b/Data/ICC005/ICC005-ATP.xlsx
@@ -1,250 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\student\student07\Measure\Data\ICC005\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58524A88-236B-496B-A82B-969312DB051F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>白芍浓度</t>
+  </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>白芍浓度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>差值</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NC</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>F2</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATP</t>
+  </si>
+  <si>
+    <t>均值</t>
   </si>
   <si>
     <t>F3</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>F4</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>F5</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>G5</t>
   </si>
   <si>
     <t>F6</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>F7</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>F8</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>G8</t>
   </si>
   <si>
     <t>F9</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>F10</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>F11</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>B11</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>C11</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>D11</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>E11</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>G3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>G4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>G5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>G6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>G7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>G8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F9</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F11</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>G9</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>G10</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>G11</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>均值</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -267,39 +129,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -386,6 +236,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -420,6 +271,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -454,20 +306,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -589,30 +437,71 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="16.571428571428573" customWidth="1"/>
+    <col min="2" max="2" width="16.714285714285715" customWidth="1"/>
+    <col min="3" max="3" width="14.571428571428571" customWidth="1"/>
+    <col min="4" max="4" width="14.428571428571429" customWidth="1"/>
+    <col min="5" max="5" width="11.571428571428571" customWidth="1"/>
+    <col min="6" max="6" width="13.571428571428571" customWidth="1"/>
+    <col min="7" max="7" width="18.142857142857142" customWidth="1"/>
+    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="C1" s="1">
         <v>20230701</v>
@@ -620,626 +509,466 @@
       <c r="D1" s="1">
         <v>20230703</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>150</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>19</v>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>0.40927631046611601</v>
+        <v>0.409276310466116</v>
       </c>
       <c r="D2">
         <v>-1.87256279253764</v>
       </c>
       <c r="E2">
         <f>D2-C2</f>
-        <v>-2.2818391030037559</v>
-      </c>
-      <c r="F2" s="9">
+      </c>
+      <c r="F2" s="3">
         <v>4212000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4" t="s">
-        <v>20</v>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C3">
         <v>1.10895470036196</v>
       </c>
       <c r="D3">
-        <v>-1.2923053220775149</v>
+        <v>-1.292305322077515</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E19" si="0">D3-C3</f>
-        <v>-2.4012600224394749</v>
-      </c>
-      <c r="F3" s="9">
+        <f>D3-C3</f>
+      </c>
+      <c r="F3" s="3">
         <v>4482000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4" t="s">
-        <v>21</v>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>1.6336911510973859</v>
+        <v>1.633691151097386</v>
       </c>
       <c r="D4">
         <v>-0.1124485085895376</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>-1.7461396596869236</v>
+        <f>D4-C4</f>
       </c>
       <c r="F4">
         <v>2923000</v>
       </c>
       <c r="G4">
-        <v>-2.2719773810000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>-2.271977381</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1.125643031019643</v>
       </c>
       <c r="D5">
-        <v>-1.4043896609464821</v>
+        <v>-1.404389660946482</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>-2.5300326919661251</v>
+        <f>D5-C5</f>
       </c>
       <c r="F5">
         <v>2974000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4" t="s">
-        <v>23</v>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>0.90254129422338103</v>
+        <v>0.902541294223381</v>
       </c>
       <c r="D6">
-        <v>-1.4980741317252779</v>
+        <v>-1.498074131725278</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
-        <v>-2.4006154259486587</v>
+        <f>D6-C6</f>
       </c>
       <c r="F6">
         <v>1661000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4" t="s">
-        <v>24</v>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>0.13278554559568451</v>
+        <v>0.1327855455956845</v>
       </c>
       <c r="D7">
-        <v>-1.3711814559353439</v>
+        <v>-1.371181455935344</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>-1.5039670015310285</v>
+        <f>D7-C7</f>
       </c>
       <c r="F7">
         <v>2941000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>225</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>25</v>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>-8.6010078468743867E-2</v>
+        <v>-0.08601007846874387</v>
       </c>
       <c r="D8">
-        <v>-1.1139146249938641</v>
+        <v>-1.113914624993864</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>-1.0279045465251202</v>
+        <f>D8-C8</f>
       </c>
       <c r="F8">
         <v>2658000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4" t="s">
-        <v>26</v>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>2.8502327454741909</v>
+        <v>2.850232745474191</v>
       </c>
       <c r="D9">
-        <v>0.77631827673754472</v>
+        <v>0.7763182767375447</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>-2.0739144687366462</v>
+        <f>D9-C9</f>
       </c>
       <c r="F9">
         <v>2197000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4" t="s">
-        <v>27</v>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C10">
         <v>1.741293864877596</v>
       </c>
       <c r="D10">
-        <v>-0.83624728118347447</v>
+        <v>-0.8362472811834745</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>-2.5775411460610704</v>
+        <f>D10-C10</f>
       </c>
       <c r="F10">
         <v>2499000</v>
       </c>
       <c r="G10">
-        <v>-0.76953259200000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4" t="s">
-        <v>28</v>
+        <v>-0.769532592</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>0.66630958082248604</v>
+        <v>0.666309580822486</v>
       </c>
       <c r="D11">
-        <v>-1.0071061555435361</v>
+        <v>-1.007106155543536</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
-        <v>-1.6734157363660223</v>
-      </c>
-      <c r="F11" s="9">
+        <f>D11-C11</f>
+      </c>
+      <c r="F11" s="3">
         <v>3192000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4" t="s">
-        <v>29</v>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>0.43409388611196081</v>
+        <v>0.4340938861119608</v>
       </c>
       <c r="D12">
-        <v>-0.93368428999012154</v>
+        <v>-0.9336842899901215</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
-        <v>-1.3677781761020824</v>
-      </c>
-      <c r="F12" s="9">
+        <f>D12-C12</f>
+      </c>
+      <c r="F12" s="3">
         <v>4570000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>0.98567436313889634</v>
+        <v>0.9856743631388963</v>
       </c>
       <c r="D13">
-        <v>-0.77174513515051324</v>
+        <v>-0.7717451351505132</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
-        <v>-1.7574194982894096</v>
+        <f>D13-C13</f>
       </c>
       <c r="F13">
         <v>1822000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>300</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>31</v>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C14">
-        <v>0.25618296926669881</v>
+        <v>0.2561829692666988</v>
       </c>
       <c r="D14">
-        <v>-1.5003489325844011</v>
+        <v>-1.500348932584401</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
-        <v>-1.7565319018510999</v>
+        <f>D14-C14</f>
       </c>
       <c r="F14">
         <v>1780000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4" t="s">
-        <v>32</v>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C15">
         <v>-0.4754708896779426</v>
       </c>
       <c r="D15">
-        <v>-1.2408208055276151</v>
+        <v>-1.240820805527615</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
-        <v>-0.76534991584967249</v>
-      </c>
-      <c r="F15" s="9">
+        <f>D15-C15</f>
+      </c>
+      <c r="F15" s="3">
         <v>3113000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4" t="s">
-        <v>33</v>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C16">
-        <v>-6.5768731856340754E-3</v>
+        <v>-0.006576873185634075</v>
       </c>
       <c r="D16">
-        <v>-0.92668536145378688</v>
+        <v>-0.9266853614537869</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
-        <v>-0.92010848826815284</v>
+        <f>D16-C16</f>
       </c>
       <c r="F16">
         <v>1647000</v>
       </c>
       <c r="G16">
-        <v>-0.45046807300000002</v>
+        <v>-0.450468073</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4" t="s">
-        <v>34</v>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>0.19803016554361949</v>
+        <v>0.1980301655436195</v>
       </c>
       <c r="D17">
         <v>1.263921667253977</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
-        <v>1.0658915017103576</v>
-      </c>
-      <c r="F17" s="9">
+        <f>D17-C17</f>
+      </c>
+      <c r="F17" s="3">
         <v>3397000</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4" t="s">
-        <v>35</v>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C18">
         <v>1.336862415126195</v>
       </c>
       <c r="D18">
-        <v>-8.3279330421235365E-2</v>
+        <v>-0.08327933042123536</v>
       </c>
       <c r="E18">
-        <f t="shared" si="0"/>
-        <v>-1.4201417455474303</v>
+        <f>D18-C18</f>
       </c>
       <c r="F18">
         <v>2840000</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="4" t="s">
-        <v>36</v>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>0.92663533589380798</v>
+        <v>0.926635335893808</v>
       </c>
       <c r="D19">
-        <v>-0.21559567301848101</v>
+        <v>-0.215595673018481</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
-        <v>-1.1422310089122889</v>
+        <f>D19-C19</f>
       </c>
       <c r="F19">
         <v>2002000</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.16685012505365501</v>
-      </c>
-      <c r="D20" s="2">
-        <v>3.5856870228598789</v>
-      </c>
-      <c r="E20" s="4">
-        <v>3.4188368978062238</v>
-      </c>
-      <c r="F20" s="7">
-        <v>26980000</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
-        <v>-1.065695675660415</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.70445205748466166</v>
-      </c>
-      <c r="E21" s="4">
-        <v>1.7701477331450768</v>
-      </c>
-      <c r="F21" s="2">
-        <v>14110000</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="2">
-        <v>-0.33161715935378278</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1.494775643123851</v>
-      </c>
-      <c r="E22" s="4">
-        <v>1.8263928024776339</v>
-      </c>
-      <c r="F22" s="2">
-        <v>13740000</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2">
-        <v>-0.58243945627520821</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.98186468189163867</v>
-      </c>
-      <c r="E23" s="4">
-        <v>1.5643041381668468</v>
-      </c>
-      <c r="F23" s="2">
-        <v>17250000</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2">
-        <v>-0.87221360417711336</v>
-      </c>
-      <c r="D24" s="2">
-        <v>2.99198872164146</v>
-      </c>
-      <c r="E24" s="4">
-        <v>3.8642023258185736</v>
-      </c>
-      <c r="F24" s="7">
-        <v>20320000</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2">
-        <v>-0.91207513077618374</v>
-      </c>
-      <c r="D25" s="2">
-        <v>2.124234356773409</v>
-      </c>
-      <c r="E25" s="4">
-        <v>3.0363094875495928</v>
-      </c>
-      <c r="F25" s="7">
-        <v>20000000</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="2">
-        <v>-0.88420077180045209</v>
-      </c>
-      <c r="D26" s="2">
-        <v>3.2200313326780501</v>
-      </c>
-      <c r="E26" s="4">
-        <v>4.104232104478502</v>
-      </c>
-      <c r="F26" s="2">
-        <v>17170000</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="2">
-        <v>-1.1181511489925771</v>
-      </c>
-      <c r="D27" s="2">
-        <v>1.5796111772489181</v>
-      </c>
-      <c r="E27" s="4">
-        <v>2.6977623262414951</v>
-      </c>
-      <c r="F27" s="2">
-        <v>15830000</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2">
-        <v>-0.49020749604420782</v>
-      </c>
-      <c r="D28" s="2">
-        <v>4.4123076399552366</v>
-      </c>
-      <c r="E28" s="4">
-        <v>4.9025151359994448</v>
-      </c>
-      <c r="F28" s="7">
-        <v>21910000</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="2">
-        <v>-1.79811822813399</v>
-      </c>
-      <c r="D29" s="2">
-        <v>1.6180873718270981</v>
-      </c>
-      <c r="E29" s="4">
-        <v>3.4162055999610881</v>
-      </c>
-      <c r="F29" s="2">
-        <v>14700000</v>
-      </c>
+      <c r="A29" s="2"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0.3060310874789185</v>
-      </c>
-      <c r="D30" s="2">
-        <v>2.55744913699432</v>
-      </c>
-      <c r="E30" s="4">
-        <v>2.2514180495154017</v>
-      </c>
-      <c r="F30" s="7">
-        <v>11180000</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="2">
-        <v>-0.15531924158749311</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2.7231554906421129</v>
-      </c>
-      <c r="E31" s="4">
-        <v>2.878474732229606</v>
-      </c>
-      <c r="F31" s="2">
-        <v>13930000</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="2">
-        <v>-1.0046174246887229</v>
-      </c>
-      <c r="D32" s="2">
-        <v>0.32564426221897458</v>
-      </c>
-      <c r="E32" s="4">
-        <v>1.3302616869076975</v>
-      </c>
-      <c r="F32" s="7">
-        <v>11240000</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1.5452442207564591E-2</v>
-      </c>
-      <c r="D33" s="2">
-        <v>1.5133869301615031</v>
-      </c>
-      <c r="E33" s="4">
-        <v>1.4979344879539385</v>
-      </c>
-      <c r="F33" s="2">
-        <v>12840000</v>
-      </c>
+      <c r="A33" s="2"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1248,7 +977,7 @@
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="A20:A33"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>